--- a/LoanOfficer-A/2023/140 sunanda.xlsx
+++ b/LoanOfficer-A/2023/140 sunanda.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -831,7 +831,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>96000</v>
+        <v>95000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1133,9 +1133,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>45946</v>
+      </c>
+      <c r="C11" s="4">
+        <v>500</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>
@@ -1159,9 +1165,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>45949</v>
+      </c>
+      <c r="C12" s="4">
+        <v>500</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>

--- a/LoanOfficer-A/2023/140 sunanda.xlsx
+++ b/LoanOfficer-A/2023/140 sunanda.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -831,7 +831,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>5000</v>
+        <v>6500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>95000</v>
+        <v>93500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1197,9 +1197,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>45958</v>
+      </c>
+      <c r="C13" s="4">
+        <v>500</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
@@ -1223,9 +1229,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>45962</v>
+      </c>
+      <c r="C14" s="4">
+        <v>500</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1249,9 +1261,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45967</v>
+      </c>
+      <c r="C15" s="4">
+        <v>500</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>

--- a/LoanOfficer-A/2023/140 sunanda.xlsx
+++ b/LoanOfficer-A/2023/140 sunanda.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -831,7 +831,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>6500</v>
+        <v>7000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>93500</v>
+        <v>93000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1293,9 +1293,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45980</v>
+      </c>
+      <c r="C16" s="4">
+        <v>500</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>

--- a/LoanOfficer-A/2023/140 sunanda.xlsx
+++ b/LoanOfficer-A/2023/140 sunanda.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -831,7 +831,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>7000</v>
+        <v>7500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>93000</v>
+        <v>92500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1325,9 +1325,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45999</v>
+      </c>
+      <c r="C17" s="4">
+        <v>500</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>

--- a/LoanOfficer-A/2023/140 sunanda.xlsx
+++ b/LoanOfficer-A/2023/140 sunanda.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'MD50000.15-DEC'!$A$3:$N$32</definedName>
   </definedNames>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -831,7 +831,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>7500</v>
+        <v>8000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>92500</v>
+        <v>92000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1357,9 +1357,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>46020</v>
+      </c>
+      <c r="C18" s="4">
+        <v>500</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>

--- a/LoanOfficer-A/2023/140 sunanda.xlsx
+++ b/LoanOfficer-A/2023/140 sunanda.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -831,7 +831,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>92000</v>
+        <v>91000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1389,9 +1389,15 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>46116</v>
+      </c>
+      <c r="C19" s="4">
+        <v>500</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>
@@ -1415,9 +1421,15 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="3">
+        <v>46144</v>
+      </c>
+      <c r="C20" s="4">
+        <v>500</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
       <c r="E20" s="1">
         <v>48</v>
       </c>
